--- a/maestros.xlsx
+++ b/maestros.xlsx
@@ -9,10 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="campos_localidades" sheetId="2" r:id="rId1"/>
+    <sheet name="socios" sheetId="3" r:id="rId2"/>
+    <sheet name="especies" sheetId="4" r:id="rId3"/>
+    <sheet name="estado_cupo" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="339">
   <si>
     <t>Campo</t>
   </si>
@@ -969,6 +972,78 @@
   </si>
   <si>
     <t>Yerua</t>
+  </si>
+  <si>
+    <t>Socio</t>
+  </si>
+  <si>
+    <t>Bioceres Semillas SAU</t>
+  </si>
+  <si>
+    <t>CENTRO AGROPECUARIO MODELO S.A.</t>
+  </si>
+  <si>
+    <t>Cereales Quemu SA</t>
+  </si>
+  <si>
+    <t>Enrique M Baya Casal SA</t>
+  </si>
+  <si>
+    <t>Kerube SA</t>
+  </si>
+  <si>
+    <t>Lartirigoyen y Cia. S.A.</t>
+  </si>
+  <si>
+    <t>NVD PARTICIPACIONES S.A</t>
+  </si>
+  <si>
+    <t>Partes Iguales SH</t>
+  </si>
+  <si>
+    <t>Siner</t>
+  </si>
+  <si>
+    <t>Sovoilar SA</t>
+  </si>
+  <si>
+    <t>Especie</t>
+  </si>
+  <si>
+    <t>Soja</t>
+  </si>
+  <si>
+    <t>Maíz</t>
+  </si>
+  <si>
+    <t>Girasol</t>
+  </si>
+  <si>
+    <t>Girasol Oleico</t>
+  </si>
+  <si>
+    <t>Trigo</t>
+  </si>
+  <si>
+    <t>Cebada</t>
+  </si>
+  <si>
+    <t>Pisingallo</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Cancelado</t>
+  </si>
+  <si>
+    <t>Solicitado</t>
+  </si>
+  <si>
+    <t>Confirmado con Cupo</t>
+  </si>
+  <si>
+    <t>Confirmado sin Cupo</t>
   </si>
 </sst>
 </file>
@@ -3040,4 +3115,163 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>325</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:A11">
+    <sortCondition ref="A2"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/maestros.xlsx
+++ b/maestros.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="campos_localidades" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="340">
   <si>
     <t>Campo</t>
   </si>
@@ -1044,6 +1044,9 @@
   </si>
   <si>
     <t>Confirmado sin Cupo</t>
+  </si>
+  <si>
+    <t>Espartina</t>
   </si>
 </sst>
 </file>
@@ -3119,7 +3122,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.28515625" bestFit="1" customWidth="1"/>
@@ -3152,36 +3155,41 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>325</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:A11">
+  <sortState ref="A2:A12">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
